--- a/output/instructor/Variation 2 Answer Key.xlsx
+++ b/output/instructor/Variation 2 Answer Key.xlsx
@@ -4822,7 +4822,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Georgia</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">

--- a/output/instructor/Variation 2 Answer Key.xlsx
+++ b/output/instructor/Variation 2 Answer Key.xlsx
@@ -2306,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2330,7 +2330,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>For each campus area, what is the median price per square foot in each distance band? In most areas, does price per square foot fall as the distance from campus grows? Name any area where it does not.</t>
+          <t>For each campus area, what is the median price per square foot in each distance band? In most areas, does price per square foot fall as the distance from campus grows? Say what you count as falling, and name any area where it does not.</t>
         </is>
       </c>
     </row>
@@ -3178,251 +3178,334 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Areas that fall under three common rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Rule for "falls"</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Areas that fall</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Areas that do not fall</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Each band with enough sales is lower than the one before</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Florida, Georgia, Illinois, Iowa, Purdue and UW-Madison</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The farthest band with enough sales is lower than the nearest, and no step rises by more than 5% (the key's rule)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Florida, Illinois and Purdue</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>The farthest band with enough sales is lower than the nearest</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Students must say what they count as falling. Mark the answer against the student's own rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Model answer</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Yes, in most areas. Price per square foot is highest within 1 mile of campus in 8 of 11 areas, and it falls with distance in 8: at every step in Michigan, Penn State, UC Davis, UNC and Virginia, and overall, with no rise between neighboring bands above 5.0%, in Georgia, Iowa and UW-Madison.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>It does not fall in Florida, Illinois and Purdue. Illinois is the clearest exception: its highest band is 5 to under 10 miles ($198.20, against $159.98 under 1 mile).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Nine of the 55 cells have fewer than 20 sales, all in the outer bands, and show "fewer than 20 sales" or no sales.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Common wrong answers</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>All areas pooled into one line. Pooling mixes areas with different price levels. The outer bands are dominated by a few areas, so the pooled line rises again even though most areas fall.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>All areas pooled</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Median price per sq ft</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Under 1 mile</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B64" s="7" t="n">
         <v>1465</v>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C64" s="9" t="n">
         <v>281.4</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>1 to under 2 miles</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B65" s="7" t="n">
         <v>5234</v>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C65" s="9" t="n">
         <v>238.33</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2 to under 5 miles</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>18554</v>
-      </c>
-      <c r="C59" s="9" t="n">
-        <v>201.56</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>5 to under 10 miles</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n">
-        <v>9520</v>
-      </c>
-      <c r="C60" s="9" t="n">
-        <v>217.65</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>10 miles or more</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="n">
-        <v>248</v>
-      </c>
-      <c r="C61" s="9" t="n">
-        <v>207.65</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Small cells shown. These medians rest on fewer than 20 sales and must be replaced by "fewer than 20 sales".</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Cells that must not show a figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Campus area</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Median shown in error</t>
-        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>University of California, Davis</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>5 to under 10 miles</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="9" t="n">
-        <v>610.78</v>
+          <t>2 to under 5 miles</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>18554</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>201.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>10 miles or more</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>143.38</v>
+          <t>5 to under 10 miles</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>9520</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>217.65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
           <t>10 miles or more</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>206.18</v>
+      <c r="B68" s="7" t="n">
+        <v>248</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>207.65</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Small cells shown. These medians rest on fewer than 20 sales and must be replaced by "fewer than 20 sales".</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Each reportable cell: within $1.00.</t>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Cells that must not show a figure</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Every cell with 1 to 19 sales shows "fewer than 20 sales". A cell with no sales may show that, a dash or "no sales".</t>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Campus area</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Median shown in error</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>The answer says yes for most areas and names Illinois. Naming Florida and Purdue as well is correct. Naming an area that falls at every step (Michigan, Penn State, UC Davis, UNC and Virginia) is wrong.</t>
+          <t>University of California, Davis</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5 to under 10 miles</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>610.78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10 miles or more</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>143.38</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>University of Wisconsin-Madison</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10 miles or more</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>206.18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Each reportable cell: within $1.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Every cell with 1 to 19 sales shows "fewer than 20 sales". A cell with no sales may show that, a dash or "no sales".</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>The answer states a rule for "falls" and applies it correctly; the table above gives the result under three common rules. Under each of them most areas fall, except under the strictest rule, where 5 of 11 fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Every rule names Illinois. Naming an area that falls at every step (Michigan, Penn State, UC Davis, UNC and Virginia) is wrong under any rule.</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Across all areas, what is the median days on market for each calendar month in which homes were listed? Use only homes listed from April 1, 2023 through March 31, 2025, so that each calendar month covers exactly two years. Group them by the month of list_date. Which months are fastest, and which are slowest?</t>
+          <t>Across all areas, pooled together, what is the median days on market for each calendar month in which homes were listed? Use only homes listed from April 1, 2023 through March 31, 2025, so that each calendar month covers exactly two years. Group them by the month of list_date. Which months are fastest, and which are slowest?</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4131,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>For each campus area, what is the median ratio of tax_assessed_value to sale_price, for valid sales with an assessed value above 0? Which areas are far from 1, and what could explain the gap?</t>
+          <t>For each campus area, what is the median ratio of tax_assessed_value to sale_price, for valid sales with an assessed value above 0? Which areas are far from 1 (say what you count as far), and what could explain the gap? Cite a source for any explanation.</t>
         </is>
       </c>
     </row>
@@ -4668,14 +4751,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Names Penn State and Michigan as far from 1. Naming UC Davis as far from 1 is wrong.</t>
+          <t>Names Penn State and Michigan as far from 1, with a stated threshold. Naming other areas is correct only if they meet the student's own threshold; the next closest is Purdue at 0.78. Naming UC Davis as far from 1 is wrong under any threshold.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The explanation must rest on how each state assesses property, with a source. A claim that homes there sell far above their value earns no credit.</t>
+          <t>The explanation must rest on how each state assesses property, and the case asks for a source. A claim that homes there sell far above their value earns no credit.</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4798,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Group sales by street address, city, state and ZIP code. In each campus area, how many addresses have more than one sale, and how many sales do they cover? How does the median miles_to_campus of those sales compare with that of all other sales?</t>
+          <t>Group sales by street address, city, state and ZIP code. In each campus area, how many addresses have more than one sale, and how many sales do they cover? How does the median miles_to_campus of those sales compare with that of all other sales, across all areas and within each area?</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5236,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Counts: exact. 103 addresses and 240 sales in total, and each area's counts as in the table. For areas with fewer than 20 such sales, showing the count or "fewer than 20 sales" are both correct.</t>
+          <t>Counts: exact. 103 addresses and 240 sales in total, and each area's counts as in the table. Counts are always shown, even for small areas.</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5250,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full credit needs the overall comparison and the observation that it differs by area.</t>
+          <t>The question asks for the comparison across all areas and within each area, so full credit needs both, and the observation that the two areas with enough sales point in opposite directions.</t>
         </is>
       </c>
     </row>

--- a/output/instructor/Variation 2 Answer Key.xlsx
+++ b/output/instructor/Variation 2 Answer Key.xlsx
@@ -329,7 +329,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2781300"/>
+    <ext cx="5905500" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>888500</v>
+        <v>889000</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>492.58</v>
+        <v>492.71</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>725000</v>
@@ -838,7 +838,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>280.25</v>
@@ -854,19 +854,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2853</v>
+        <v>2774</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>625000</v>
+        <v>615000</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2851</v>
+        <v>2772</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>272.35</v>
+        <v>270.03</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>3</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>571000</v>
@@ -888,10 +888,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>259.07</v>
+        <v>259.11</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>4</v>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>5707</v>
+        <v>5706</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>434020</v>
+        <v>434010</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>5706</v>
+        <v>5705</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>249.16</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2815</v>
+        <v>2813</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>370000</v>
@@ -963,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>196.82</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5630</v>
+        <v>5629</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>355000</v>
@@ -988,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5624</v>
+        <v>5623</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>203.24</v>
@@ -1082,7 +1082,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>UC Davis is highest on both measures, with a median sale price of $888,500 and $492.58 per square foot. Illinois is lowest on both, at $245,000 and $150.30.</t>
+          <t>UC Davis is highest on both measures, with a median sale price of $889,000 and $492.71 per square foot. Illinois is lowest on both, at $245,000 and $150.30.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         <v>725000</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>825203</v>
+        <v>825205</v>
       </c>
     </row>
     <row r="30">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>888500</v>
+        <v>889000</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>976367</v>
+        <v>976896</v>
       </c>
     </row>
     <row r="31">
@@ -1199,7 +1199,7 @@
         <v>355000</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>405906</v>
+        <v>405889</v>
       </c>
     </row>
     <row r="32">
@@ -1212,7 +1212,7 @@
         <v>370000</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>491409</v>
+        <v>491552</v>
       </c>
     </row>
     <row r="33">
@@ -1238,7 +1238,7 @@
         <v>571000</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>657369</v>
+        <v>657210</v>
       </c>
     </row>
     <row r="35">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>625000</v>
+        <v>615000</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>797754</v>
+        <v>795448</v>
       </c>
     </row>
     <row r="36">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>434020</v>
+        <v>434010</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>503439</v>
+        <v>503387</v>
       </c>
     </row>
     <row r="38">
@@ -1368,10 +1368,10 @@
         <v>280.25</v>
       </c>
       <c r="C43" s="9" t="n">
-        <v>277.67</v>
+        <v>277.57</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>299.76</v>
+        <v>299.72</v>
       </c>
       <c r="E43" s="9" t="n">
         <v>280.43</v>
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>492.58</v>
+        <v>492.71</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>482.75</v>
+        <v>482.63</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>500.31</v>
+        <v>500.44</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>492.58</v>
+        <v>492.71</v>
       </c>
     </row>
     <row r="45">
@@ -1409,7 +1409,7 @@
         <v>202.16</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>210.27</v>
+        <v>210.28</v>
       </c>
       <c r="E45" s="9" t="n">
         <v>203.32</v>
@@ -1428,7 +1428,7 @@
         <v>198.76</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>220.92</v>
+        <v>220.94</v>
       </c>
       <c r="E46" s="9" t="n">
         <v>209.3</v>
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>259.07</v>
+        <v>259.11</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>256.98</v>
+        <v>257.09</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>281.39</v>
+        <v>281.41</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>259.22</v>
+        <v>259.28</v>
       </c>
     </row>
     <row r="49">
@@ -1479,16 +1479,16 @@
         </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>272.35</v>
+        <v>270.03</v>
       </c>
       <c r="C49" s="9" t="n">
-        <v>260.53</v>
+        <v>257.54</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>300.23</v>
+        <v>298.89</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>272.37</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="50">
@@ -1504,7 +1504,7 @@
         <v>243.28</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>267.47</v>
+        <v>267.46</v>
       </c>
       <c r="E50" s="9" t="n">
         <v>249.16</v>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5707</v>
+        <v>5706</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4628</v>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>2450</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>2854</v>
+        <v>2775</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>2056</v>
@@ -1692,7 +1692,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.28</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="11">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2411</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>792</v>
@@ -1768,7 +1768,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="15">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5630</v>
+        <v>5629</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>4505</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="D17" t="n">
         <v>27</v>
@@ -2172,7 +2172,7 @@
         <v>0.201</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="44">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="45">
@@ -2211,7 +2211,7 @@
         <v>0.19</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="47">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>0.28</v>
+        <v>0.259</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>0.274</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="50">
@@ -2393,7 +2393,7 @@
         <v>365.72</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>268.46</v>
+        <v>268.44</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>231.4</v>
@@ -2420,7 +2420,7 @@
         <v>191.27</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>213.03</v>
+        <v>213.05</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>193.37</v>
@@ -2482,7 +2482,7 @@
         <v>427.52</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>331.77</v>
+        <v>332.21</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>237.26</v>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>400.2</v>
+        <v>400.18</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>311.09</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>284.47</v>
+        <v>284.53</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>265.15</v>
@@ -2525,19 +2525,19 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>342.35</v>
+        <v>340.5</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>317.04</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>268.06</v>
+        <v>266.83</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>258.75</v>
+        <v>253.95</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>223.04</v>
+        <v>220.23</v>
       </c>
     </row>
     <row r="14">
@@ -2553,10 +2553,10 @@
         <v>280.68</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>192.2</v>
+        <v>192.18</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>185.46</v>
+        <v>185.52</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>497.78</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>485.47</v>
+        <v>485.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>286</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2744</v>
@@ -2717,7 +2717,7 @@
         <v>2711</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>33</v>
@@ -2777,7 +2777,7 @@
         <v>179</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1624</v>
@@ -2796,13 +2796,13 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>420</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>959</v>
@@ -2818,19 +2818,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>466</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1262</v>
+        <v>1234</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>912</v>
+        <v>865</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28">
@@ -2846,10 +2846,10 @@
         <v>354</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>358</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>8</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C64" s="9" t="n">
-        <v>281.4</v>
+        <v>281.26</v>
       </c>
     </row>
     <row r="65">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>5234</v>
+        <v>5233</v>
       </c>
       <c r="C65" s="9" t="n">
-        <v>238.33</v>
+        <v>238.43</v>
       </c>
     </row>
     <row r="66">
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>18554</v>
+        <v>18522</v>
       </c>
       <c r="C66" s="9" t="n">
-        <v>201.56</v>
+        <v>201.44</v>
       </c>
     </row>
     <row r="67">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>9520</v>
+        <v>9471</v>
       </c>
       <c r="C67" s="9" t="n">
-        <v>217.65</v>
+        <v>217.34</v>
       </c>
     </row>
     <row r="68">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>207.65</v>
+        <v>207.28</v>
       </c>
     </row>
     <row r="70">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.33</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>5498</v>
+        <v>5497</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>0.83</v>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>5665</v>
+        <v>5664</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>0.88</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>2858</v>
+        <v>2856</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>0.9</v>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2661</v>
+        <v>2583</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>0.97</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>1</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>1</v>
@@ -4687,7 +4687,7 @@
         <v>3.01</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>135.74</v>
+        <v>135.79</v>
       </c>
     </row>
     <row r="43">
@@ -4703,7 +4703,7 @@
         <v>0.99</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>1.03</v>
@@ -4846,52 +4846,54 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>The Pennsylvania State University</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Pennsylvania State University</t>
+          <t>The University of North Carolina at Chapel Hill</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5</v>
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fewer than 20 sales</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The University of North Carolina at Chapel Hill</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4899,118 +4901,118 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>fewer than 20 sales</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>Purdue University</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>fewer than 20 sales</t>
+          <t>no sales</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>University of California, Davis</t>
+          <t>The University of Iowa</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>fewer than 20 sales</t>
+          <t>no sales</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Davis</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>no sales</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>fewer than 20 sales</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>University of Georgia</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>fewer than 20 sales</t>
+          <t>no sales</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -5025,13 +5027,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>The University of Iowa</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
@@ -5046,13 +5048,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -5067,7 +5069,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18">
@@ -5077,13 +5079,13 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="n">
         <v>3.4</v>
@@ -5099,21 +5101,21 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>In all, 103 addresses have more than one sale, covering 240 sales. They are concentrated in two areas: Virginia (80 addresses, 160 sales) and Penn State (13 addresses, 60 sales). Purdue, Iowa and Illinois have none, and every other area has 3 or fewer such addresses.</t>
+          <t>In all, 16 addresses have more than one sale, covering 66 sales. Almost all are around Penn State (13 addresses, 60 sales). UNC, Florida and Virginia have one such address each, and Purdue, Iowa, UC Davis, Georgia, Illinois, Michigan and UW-Madison have none.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Across all areas, those sales sit a median 4.1 miles from campus, against 3.4 for all other sales. That overall figure mixes two opposite patterns. Around Penn State, the repeated addresses are close to campus (0.5 miles against 2.2). Around Virginia, they are farther out (6.7 against 3.3). The other areas have fewer than 20 such sales.</t>
+          <t>Across all areas, those sales sit a median 0.5 miles from campus, against 3.4 for all other sales. Within an area, only Penn State has 20 or more such sales. There they sit much closer to campus than other sales, 0.5 miles against 2.2, which fits condo and apartment buildings near campus. The other areas have fewer than 20 such sales.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Instructor note: what the repeated addresses are. The description sheet calls all 240 rows separate condo or apartment units. That holds in State College. But 87 of the 103 addresses (174 rows) meet the build notes' own test for one sale recorded twice: two rows, prices within 1% and sale dates within 90 days. Of these, 79 are in Virginia, and 78 of those are homes built in 2023 or later. In 79 of the 87 pairs, one row carries the listing dates and the other carries the county's parcel number and assessed value, so the build's parcel check missed them. Their coordinates differ too, which is why Virginia's repeated-address sales look far from campus. Do not mark down a student who spots this and explains it. The figures above follow the question's definition, which counts every row.</t>
+          <t>Instructor note: what the repeated addresses are. The 60 sales around Penn State are condo and apartment units in 13 buildings, each unit with its own parcel number. The other 6 sales are pairs: two different sales, at different prices and about a year or more apart, at each of 3 homes built in 2023 or 2024. The description sheet explains both. A student who says the repeated addresses are mostly condo buildings close to campus is right.</t>
         </is>
       </c>
     </row>
@@ -5167,13 +5169,13 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="D29" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
@@ -5183,13 +5185,13 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>312</v>
+        <v>138</v>
       </c>
       <c r="D30" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
@@ -5217,13 +5219,13 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -5236,7 +5238,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Counts: exact. 103 addresses and 240 sales in total, and each area's counts as in the table. Counts are always shown, even for small areas.</t>
+          <t>Counts: exact. 16 addresses and 66 sales in total, and each area's counts as in the table. Counts are always shown, even for small areas.</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5252,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>The question asks for the comparison across all areas and within each area, so full credit needs both, and the observation that the two areas with enough sales point in opposite directions.</t>
+          <t>The question asks for the comparison across all areas and within each area, so full credit needs both: the overall comparison, Penn State's comparison, and "fewer than 20 sales" for each other area that has such sales.</t>
         </is>
       </c>
     </row>
